--- a/stories/arbres/ATOM-REL.AMI.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Romy est au parc avec maman. Elle joue au bac à sable. Nadir arrive. Romy dit : tu veux jouer avec nous ? C'est inviter. Nadir dit : non, merci. Romy écoute. Accepter un non, c'est possible. Elle dit : d'accord. Elle continue son château. Maman sourit. Plus tard, à la maison, Romy prépare de la pâte. Lila dessine. Romy dit : tu veux jouer avec nous ? Lila dit : non, je dessine. Romy se souvient. Accepter un non. Elle dit : d'accord. Elle pétrit la pâte. Maman dit : tu as su inviter. Tu as su accepter un non. Même leçon, autre lieu.</t>
+          <t>Romy est au parc avec maman. Elle joue au bac à sable. Nadir arrive. Tu veux jouer avec nous ? C'est inviter. Non, merci. Romy écoute. Accepter un non, c'est possible. D'accord. Elle continue son château. Maman sourit. Plus tard, à la maison, Romy prépare de la pâte. Lila dessine. Tu veux jouer avec nous ? Non, je dessine. Romy se souvient. Accepter un non. D'accord. Elle pétrit la pâte. Tu as su inviter. Tu as su accepter un non. Même leçon, autre lieu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,21 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Romy est au parc avec maman. Elle joue au bac à sable. Nadir arrive.
+enfant-m|Tu veux jouer avec nous ? C'est inviter.
+copain|Non, merci.
+narrateur|Romy écoute. Accepter un non, c'est possible.
+narrateur|D'accord. Elle continue son château. Maman sourit. Plus tard, à la maison, Romy prépare de la pâte.
+narrateur|Lila dessine.
+enfant-m|Tu veux jouer avec nous ?
+copine|Non, je dessine.
+narrateur|Romy se souvient. Accepter un non.
+narrateur|D'accord. Elle pétrit la pâte.
+maman|Tu as su inviter. Tu as su accepter un non. Même leçon, autre lieu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Romy veut jouer. Que peut-elle dire ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Romy a invité. Au parc, puis à la maison. Elle a su accepter un non.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Romy range la pâte. Maman dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1320,6 +1325,11 @@
 maman|Tu as su inviter. Tu as su accepter un non. Même leçon, autre lieu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1513,7 @@
           <t>narrateur|Romy veut jouer. Que peut-elle dire ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,11 @@
           <t>narrateur|Romy a invité. Au parc, puis à la maison. Elle a su accepter un non.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1853,7 @@
           <t>narrateur|Romy range la pâte. Maman dit merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Romy invite, et accepte un non</t>
+          <t>Le château de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une pelle de bois a du sable. Nina invite Nino au bac, puis à la pâte. Deux fois, elle accepte un non.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Romy est au parc avec maman. Elle joue au bac à sable. Nadir arrive. Tu veux jouer avec nous ? C'est inviter. Non, merci. Romy écoute. Accepter un non, c'est possible. D'accord. Elle continue son château. Maman sourit. Plus tard, à la maison, Romy prépare de la pâte. Lila dessine. Tu veux jouer avec nous ? Non, je dessine. Romy se souvient. Accepter un non. D'accord. Elle pétrit la pâte. Tu as su inviter. Tu as su accepter un non. Même leçon, autre lieu.</t>
+          <t>Une pelle de bois a du sable collé. Le seau a un petit trou. Le bac sent le sable chaud. Un pigeon marche sur le chemin. Maman pose le panier près du banc. Le banc a des rayures d'ombre. Nina, le château attend. En ce moment, Nina creuse dans le bac. Le sable coule entre ses doigts. Il est chaud, maman. Oui. Nino arrive près des pigeons. Nina veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Non, merci. Nina écoute. Accepter un non, c'est possible. D'accord. Elle continue son château. Le seau laisse un filet de sable. Nino regarde les pigeons. Bravo, Nina. Tu as su inviter. Tu as su accepter un non. Plus tard, à la maison, la table est farinée. Ça sent la pâte tiède. Nina pétrit un morceau. Nino dessine près de la fenêtre. Tu veux jouer avec nous ? Non, je dessine. Nina se souvient. D'accord. Elle pétrit la pâte. Tu as su inviter. Tu as su accepter un non. Ici, comme au parc. Tu as fait du bon travail. La pâte est molle. Oui. La farine fait un petit nuage. Nina forme une petite tour. Nino tourne sa feuille. Tu as invité deux fois. Tu as accepté un non deux fois. D'accord. Le jeu reste doux. Un pigeon passe encore derrière la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Romy est au parc avec maman. Elle joue au bac à sable. Nadir arrive.
-enfant-m|Tu veux jouer avec nous ? C'est inviter.
+          <t>narrateur|Une pelle de bois a du sable collé.
+narrateur|Le seau a un petit trou.
+narrateur|Le bac sent le sable chaud.
+narrateur|Un pigeon marche sur le chemin.
+narrateur|Maman pose le panier près du banc.
+narrateur|Le banc a des rayures d'ombre.
+maman|Nina, le château attend.
+narrateur|En ce moment, Nina creuse dans le bac.
+narrateur|Le sable coule entre ses doigts.
+enfant-f|Il est chaud, maman.
+maman|Oui.
+narrateur|Nino arrive près des pigeons.
+narrateur|Nina veut jouer.
+maman|Tu peux inviter.
+maman|Inviter, c'est demander.
+enfant-f|Tu veux jouer avec nous ?
 copain|Non, merci.
-narrateur|Romy écoute. Accepter un non, c'est possible.
-narrateur|D'accord. Elle continue son château. Maman sourit. Plus tard, à la maison, Romy prépare de la pâte.
-narrateur|Lila dessine.
-enfant-m|Tu veux jouer avec nous ?
-copine|Non, je dessine.
-narrateur|Romy se souvient. Accepter un non.
-narrateur|D'accord. Elle pétrit la pâte.
-maman|Tu as su inviter. Tu as su accepter un non. Même leçon, autre lieu.</t>
+narrateur|Nina écoute.
+maman|Accepter un non, c'est possible.
+enfant-f|D'accord.
+narrateur|Elle continue son château.
+narrateur|Le seau laisse un filet de sable.
+narrateur|Nino regarde les pigeons.
+maman|Bravo, Nina.
+maman|Tu as su inviter.
+maman|Tu as su accepter un non.
+narrateur|Plus tard, à la maison, la table est farinée.
+narrateur|Ça sent la pâte tiède.
+narrateur|Nina pétrit un morceau.
+narrateur|Nino dessine près de la fenêtre.
+enfant-f|Tu veux jouer avec nous ?
+copain|Non, je dessine.
+narrateur|Nina se souvient.
+enfant-f|D'accord.
+narrateur|Elle pétrit la pâte.
+maman|Tu as su inviter.
+maman|Tu as su accepter un non.
+maman|Ici, comme au parc.
+maman|Tu as fait du bon travail.
+enfant-f|La pâte est molle.
+maman|Oui.
+narrateur|La farine fait un petit nuage.
+narrateur|Nina forme une petite tour.
+narrateur|Nino tourne sa feuille.
+maman|Tu as invité deux fois.
+maman|Tu as accepté un non deux fois.
+enfant-f|D'accord.
+maman|Le jeu reste doux.
+narrateur|Un pigeon passe encore derrière la vitre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1354,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Romy veut jouer. Que peut-elle dire ?</t>
+          <t>Nina veut jouer. Que peut-elle dire ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1510,7 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Romy veut jouer. Que peut-elle dire ?</t>
+          <t>narrateur|Nina veut jouer.
+narrateur|Que peut-elle dire ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1538,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Romy a invité. Au parc, puis à la maison. Elle a su accepter un non.</t>
+          <t>Nina a invité. Au parc, puis à la maison. Elle a su accepter un non. Tu as invité ? Oui, maman. Nino a dit non. Tu as accepté un non. Oui. Bravo. Tu as fait du bon travail. Nina forme une petite boule. Nino continue son dessin. C'est un oiseau. Oui. On peut inviter. On peut accepter un non. La pâte reste molle sous les doigts. La fenêtre sent encore le dehors. Le château est au parc. Oui. Tu as demandé. Tu as accepté un non. Oui, maman. Un peu de farine tombe. Ça fait un tout petit bruit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,7 +1733,31 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Romy a invité. Au parc, puis à la maison. Elle a su accepter un non.</t>
+          <t>narrateur|Nina a invité.
+narrateur|Au parc, puis à la maison.
+narrateur|Elle a su accepter un non.
+maman|Tu as invité ?
+enfant-f|Oui, maman.
+maman|Nino a dit non.
+maman|Tu as accepté un non.
+enfant-f|Oui.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Nina forme une petite boule.
+narrateur|Nino continue son dessin.
+enfant-f|C'est un oiseau.
+maman|Oui.
+maman|On peut inviter.
+maman|On peut accepter un non.
+narrateur|La pâte reste molle sous les doigts.
+narrateur|La fenêtre sent encore le dehors.
+enfant-f|Le château est au parc.
+maman|Oui.
+maman|Tu as demandé.
+maman|Tu as accepté un non.
+enfant-f|Oui, maman.
+narrateur|Un peu de farine tombe.
+narrateur|Ça fait un tout petit bruit.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1714,7 +1789,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Romy range la pâte. Maman dit merci.</t>
+          <t>On range la pâte ? Oui. Nina range la pâte dans le bol. Maman essuie la table. Il reste un peu de farine. Tu as fini de pétrir ? Oui, maman. Merci. Bravo. Nino range son crayon. Au revoir le château. Au revoir. La cuisine sent encore la pâte. Tu as su inviter, Nina. Oui. Le bol attend au milieu. La table redevient lisse.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1850,7 +1925,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Romy range la pâte. Maman dit merci.</t>
+          <t>maman|On range la pâte ?
+enfant-f|Oui.
+narrateur|Nina range la pâte dans le bol.
+narrateur|Maman essuie la table.
+narrateur|Il reste un peu de farine.
+maman|Tu as fini de pétrir ?
+enfant-f|Oui, maman.
+maman|Merci.
+maman|Bravo.
+narrateur|Nino range son crayon.
+copain|Au revoir le château.
+enfant-f|Au revoir.
+narrateur|La cuisine sent encore la pâte.
+maman|Tu as su inviter, Nina.
+enfant-f|Oui.
+narrateur|Le bol attend au milieu.
+narrateur|La table redevient lisse.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1878,7 +1969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai invité. Nino a dit non. Tu as accepté un non. Bravo, Nina. Le bol attend sur la table. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,7 +2109,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai invité.
+enfant-f|Nino a dit non.
+maman|Tu as accepté un non.
+maman|Bravo, Nina.
+narrateur|Le bol attend sur la table.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2040,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2174,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une pelle de bois a du sable collé. Le seau a un petit trou. Le bac sent le sable chaud. Un pigeon marche sur le chemin. Maman pose le panier près du banc. Le banc a des rayures d'ombre. Nina, le château attend. En ce moment, Nina creuse dans le bac. Le sable coule entre ses doigts. Il est chaud, maman. Oui. Nino arrive près des pigeons. Nina veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Non, merci. Nina écoute. Accepter un non, c'est possible. D'accord. Elle continue son château. Le seau laisse un filet de sable. Nino regarde les pigeons. Bravo, Nina. Tu as su inviter. Tu as su accepter un non. Plus tard, à la maison, la table est farinée. Ça sent la pâte tiède. Nina pétrit un morceau. Nino dessine près de la fenêtre. Tu veux jouer avec nous ? Non, je dessine. Nina se souvient. D'accord. Elle pétrit la pâte. Tu as su inviter. Tu as su accepter un non. Ici, comme au parc. Tu as fait du bon travail. La pâte est molle. Oui. La farine fait un petit nuage. Nina forme une petite tour. Nino tourne sa feuille. Tu as invité deux fois. Tu as accepté un non deux fois. D'accord. Le jeu reste doux. Un pigeon passe encore derrière la vitre.</t>
+          <t>Une pelle de bois a du sable collé. Le seau a un petit trou. Le bac sent le sable chaud. Un pigeon marche sur le chemin. Maman pose le panier près du banc. Le banc a des rayures d'ombre. Nina, le château attend. En ce moment, Nina creuse dans le bac. Le sable coule entre ses doigts. Il est chaud, maman. Oui. Nino arrive près des pigeons. Nina veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Non, merci. Nina écoute. Accepter un non, c'est possible. D'accord. Elle continue son château. Le seau laisse un filet de sable. Nino regarde les pigeons. Bravo, Nina. Tu as su inviter. Tu as su accepter un non. Plus tard, à la maison, la table est farinée. Ça sent la pâte tiède. Nina pétrit un morceau. Nino dessine près de la fenêtre. Tu veux jouer avec nous ? Non, je dessine. Nina se souvient. D'accord. Elle pétrit la pâte. Tu as su inviter. Tu as su accepter un non. Ici, comme au parc. La pâte est molle. Oui. La farine fait un petit nuage. Nina forme une petite tour. Nino tourne sa feuille. Tu as invité deux fois. Tu as accepté un non deux fois. D'accord. Le jeu reste doux. Un pigeon passe encore derrière la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Romy est au parc avec maman. Elle joue au bac à sable. Nadir arrive. Romy dit : tu veux jouer avec nous ? C'est &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Nadir dit : non, merci. Romy écoute. Accepter un non, c'est possible. Elle dit : d'accord. Elle continue son château. Maman sourit. Plus tard, à la maison, Romy prépare de la pâte. Lila dessine. Romy dit : tu veux jouer avec nous ? Lila dit : non, je dessine. Romy se souvient. Accepter un non. Elle dit : d'accord. Elle pétrit la pâte. Maman dit : tu as su inviter. Tu as su accepter un non. Même leçon, autre lieu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une pelle de bois a du sable collé. Le seau a un petit trou. Le bac sent le sable chaud. Un pigeon marche sur le chemin. Maman pose le panier près du banc. Le banc a des rayures d'ombre. Nina, le château attend. En ce moment, Nina creuse dans le bac. Le sable coule entre ses doigts. Il est chaud, maman. Oui. Nino arrive près des pigeons. Nina veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Non, merci. Nina écoute. Accepter un non, c'est possible. D'accord. Elle continue son château. Le seau laisse un filet de sable. Nino regarde les pigeons. Bravo, Nina. Tu as su inviter. Tu as su accepter un non. Plus tard, à la maison, la table est farinée. Ça sent la pâte tiède. Nina pétrit un morceau. Nino dessine près de la fenêtre. Tu veux jouer avec nous ? Non, je dessine. Nina se souvient. D'accord. Elle pétrit la pâte. Tu as su inviter. Tu as su accepter un non. Ici, comme au parc. La pâte est molle. Oui. La farine fait un petit nuage. Nina forme une petite tour. Nino tourne sa feuille. Tu as invité deux fois. Tu as accepté un non deux fois. D'accord. Le jeu reste doux. Un pigeon passe encore derrière la vitre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1362,7 +1362,6 @@
 maman|Tu as su inviter.
 maman|Tu as su accepter un non.
 maman|Ici, comme au parc.
-maman|Tu as fait du bon travail.
 enfant-f|La pâte est molle.
 maman|Oui.
 narrateur|La farine fait un petit nuage.
@@ -1409,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Romy veut jouer. Que peut-elle dire ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina veut jouer. Que peut-elle dire ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1564,7 +1563,6 @@
 narrateur|Que peut-elle dire ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1589,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a invité. Au parc, puis à la maison. Elle a su accepter un non. Tu as invité ? Oui, maman. Nino a dit non. Tu as accepté un non. Oui. Bravo. Tu as fait du bon travail. Nina forme une petite boule. Nino continue son dessin. C'est un oiseau. Oui. On peut inviter. On peut accepter un non. La pâte reste molle sous les doigts. La fenêtre sent encore le dehors. Le château est au parc. Oui. Tu as demandé. Tu as accepté un non. Oui, maman. Un peu de farine tombe. Ça fait un tout petit bruit.</t>
+          <t>Nina a invité. Au parc, puis à la maison. Elle a su accepter un non. Tu as invité ? Oui, maman. Nino a dit non. Tu as accepté un non. Oui. Bravo. Nina forme une petite boule. Nino continue son dessin. C'est un oiseau. Oui. On peut inviter. On peut accepter un non. La pâte reste molle sous les doigts. La fenêtre sent encore le dehors. Le château est au parc. Oui. Tu as demandé. Tu as accepté un non. Oui, maman. Un peu de farine tombe. Ça fait un tout petit bruit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Romy a invité. Au parc, puis à la maison. Elle a su &lt;emphasis level="moderate"&gt;accepter&lt;/emphasis&gt; un non.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a invité. Au parc, puis à la maison. Elle a su accepter un non. Tu as invité ? Oui, maman. Nino a dit non. Tu as accepté un non. Oui. Bravo. Nina forme une petite boule. Nino continue son dessin. C'est un oiseau. Oui. On peut inviter. On peut accepter un non. La pâte reste molle sous les doigts. La fenêtre sent encore le dehors. Le château est au parc. Oui. Tu as demandé. Tu as accepté un non. Oui, maman. Un peu de farine tombe. Ça fait un tout petit bruit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,7 +1740,6 @@
 maman|Tu as accepté un non.
 enfant-f|Oui.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Nina forme une petite boule.
 narrateur|Nino continue son dessin.
 enfant-f|C'est un oiseau.
@@ -1794,7 +1791,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Romy range la pâte. Maman dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range la pâte ? Oui. Nina range la pâte dans le bol. Maman essuie la table. Il reste un peu de farine. Tu as fini de pétrir ? Oui, maman. Merci. Bravo. Nino range son crayon. Au revoir le château. Au revoir. La cuisine sent encore la pâte. Tu as su inviter, Nina. Oui. Le bol attend au milieu. La table redevient lisse.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1944,7 +1941,6 @@
 narrateur|La table redevient lisse.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai invité. Nino a dit non. Tu as accepté un non. Bravo, Nina. Le bol attend sur la table. L'histoire est finie.</t>
+          <t>J'ai invité. Nino a dit non. Tu as accepté un non. Bravo, Nina. Le bol attend sur la table.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai invité. Nino a dit non. Tu as accepté un non. Bravo, Nina. Le bol attend sur la table.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2113,11 +2109,9 @@
 enfant-f|Nino a dit non.
 maman|Tu as accepté un non.
 maman|Bravo, Nina.
-narrateur|Le bol attend sur la table.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le bol attend sur la table.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2136,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2181,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Romy, Nadir, Lila, maman</t>
+          <t>Nina, Nino, maman</t>
         </is>
       </c>
     </row>
